--- a/reports/2026-08_月次実績報告/excel/第51期下期下関営業所担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期下関営業所担当者別実績.xlsx
@@ -7194,7 +7194,10 @@
         <v/>
       </c>
       <c r="J82" s="63" t="n"/>
-      <c r="K82" s="56" t="n"/>
+      <c r="K82" s="63">
+        <f>SUM(E82:J82)</f>
+        <v/>
+      </c>
       <c r="L82" s="82">
         <f>全体!L82-機械!L82</f>
         <v/>
@@ -7216,7 +7219,10 @@
         <v/>
       </c>
       <c r="Q82" s="62" t="n"/>
-      <c r="R82" s="56" t="n"/>
+      <c r="R82" s="62">
+        <f>SUM(L82:Q82)</f>
+        <v/>
+      </c>
       <c r="S82" s="103" t="n"/>
       <c r="T82" s="104" t="n"/>
       <c r="U82" s="104" t="n"/>
@@ -14305,7 +14311,10 @@
         <v>0</v>
       </c>
       <c r="J82" s="3" t="n"/>
-      <c r="K82" s="59" t="n"/>
+      <c r="K82" s="3">
+        <f>SUM(E82:J82)</f>
+        <v/>
+      </c>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="3" t="n"/>
       <c r="N82" s="3" t="n"/>
@@ -14314,7 +14323,10 @@
         <v>0</v>
       </c>
       <c r="Q82" s="3" t="n"/>
-      <c r="R82" s="56" t="n"/>
+      <c r="R82" s="3">
+        <f>SUM(L82:Q82)</f>
+        <v/>
+      </c>
       <c r="S82" s="103" t="n"/>
       <c r="T82" s="104" t="n"/>
       <c r="U82" s="104" t="n"/>
@@ -21662,7 +21674,10 @@
         <v>69.09999999999999</v>
       </c>
       <c r="J82" s="3" t="n"/>
-      <c r="K82" s="59" t="n"/>
+      <c r="K82" s="3">
+        <f>SUM(E82:J82)</f>
+        <v/>
+      </c>
       <c r="L82" s="2" t="n"/>
       <c r="M82" s="3" t="n"/>
       <c r="N82" s="80" t="n">
@@ -21675,7 +21690,10 @@
         <v>2.2</v>
       </c>
       <c r="Q82" s="3" t="n"/>
-      <c r="R82" s="56" t="n"/>
+      <c r="R82" s="3">
+        <f>SUM(L82:Q82)</f>
+        <v/>
+      </c>
       <c r="S82" s="103" t="n"/>
       <c r="T82" s="104" t="n"/>
       <c r="U82" s="104" t="n"/>
